--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E63A6CA-0C37-448C-93CF-AC832AC86119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DC4835-EA4E-4340-86BA-C2C116D64B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
   <si>
     <t>Client</t>
   </si>
@@ -150,9 +150,6 @@
     <t>10.0</t>
   </si>
   <si>
-    <t>9999.0</t>
-  </si>
-  <si>
     <t>Board of Directors</t>
   </si>
   <si>
@@ -291,9 +288,6 @@
     <t>Chris Lord</t>
   </si>
   <si>
-    <t>Drew Koecher</t>
-  </si>
-  <si>
     <t>Danielle Morello</t>
   </si>
   <si>
@@ -301,6 +295,9 @@
   </si>
   <si>
     <t>Karan Chopra</t>
+  </si>
+  <si>
+    <t>9999</t>
   </si>
 </sst>
 </file>
@@ -754,27 +751,27 @@
         <v>35</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -801,13 +798,13 @@
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s">
         <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>39</v>
@@ -825,13 +822,13 @@
         <v>27</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="U2" t="s">
         <v>30</v>
       </c>
       <c r="V2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="W2" t="s">
         <v>34</v>
@@ -840,13 +837,13 @@
         <v>36</v>
       </c>
       <c r="Y2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>39</v>
@@ -877,10 +874,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -909,22 +906,22 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -932,25 +929,25 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -989,72 +986,72 @@
   <sheetData>
     <row r="1" spans="1:21" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="U1" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1063,13 +1060,13 @@
         <v>39</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>39</v>
@@ -1114,7 +1111,7 @@
         <v>9</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DC4835-EA4E-4340-86BA-C2C116D64B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C14E8D2-85F7-4EE5-AFA5-29B81240004C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="89">
   <si>
     <t>Client</t>
   </si>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>ReferralContact</t>
-  </si>
-  <si>
-    <t>Lord Kelvin</t>
   </si>
   <si>
     <t>Agreement</t>
@@ -745,33 +742,33 @@
         <v>31</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -798,22 +795,22 @@
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s">
         <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R2" t="s">
         <v>27</v>
@@ -822,31 +819,31 @@
         <v>27</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U2" t="s">
         <v>30</v>
       </c>
       <c r="V2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -874,10 +871,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -900,54 +897,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -986,132 +983,132 @@
   <sheetData>
     <row r="1" spans="1:21" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="U1" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C14E8D2-85F7-4EE5-AFA5-29B81240004C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9542753-2AD3-47D9-B5B1-870789387C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="91">
   <si>
     <t>Client</t>
   </si>
@@ -295,6 +295,12 @@
   </si>
   <si>
     <t>9999</t>
+  </si>
+  <si>
+    <t>Techno Aide</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -955,7 +961,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="95.88671875" style="8" bestFit="1" customWidth="1"/>
@@ -978,10 +984,11 @@
     <col min="19" max="19" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.88671875" style="8"/>
     <col min="21" max="21" width="102.33203125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="8"/>
+    <col min="22" max="22" width="11" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>54</v>
       </c>
@@ -1046,12 +1053,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
@@ -1110,47 +1117,50 @@
       <c r="U2" s="7" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:21" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9542753-2AD3-47D9-B5B1-870789387C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D908E6B9-5B37-498B-A7B6-1570061D259D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>Client</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>Techno Alpha</t>
   </si>
 </sst>
 </file>
@@ -961,7 +964,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="95.88671875" style="8" bestFit="1" customWidth="1"/>
@@ -988,7 +991,7 @@
     <col min="23" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>54</v>
       </c>
@@ -1053,7 +1056,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>79</v>
       </c>
@@ -1120,47 +1123,50 @@
       <c r="V2" s="8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W2" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:22" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D908E6B9-5B37-498B-A7B6-1570061D259D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41136B89-AA16-422B-8FBB-07C735F1EEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -285,9 +285,6 @@
     <t>Chris Lord</t>
   </si>
   <si>
-    <t>Danielle Morello</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
@@ -304,6 +301,9 @@
   </si>
   <si>
     <t>Techno Alpha</t>
+  </si>
+  <si>
+    <t> Liz Hedgcock</t>
   </si>
 </sst>
 </file>
@@ -810,7 +810,7 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>38</v>
@@ -828,7 +828,7 @@
         <v>27</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="U2" t="s">
         <v>30</v>
@@ -849,7 +849,7 @@
         <v>57</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>38</v>
@@ -880,14 +880,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1061,7 +1062,7 @@
         <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
@@ -1121,10 +1122,10 @@
         <v>80</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41136B89-AA16-422B-8FBB-07C735F1EEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32759BC7-39F3-443B-BFE0-7DC2A50FCFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -51,9 +51,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -304,6 +301,9 @@
   </si>
   <si>
     <t> Liz Hedgcock</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -706,153 +706,153 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" t="s">
         <v>82</v>
       </c>
-      <c r="B2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>86</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="U2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -872,18 +872,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -907,54 +907,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -994,138 +994,138 @@
   <sheetData>
     <row r="1" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="U1" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="V2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32759BC7-39F3-443B-BFE0-7DC2A50FCFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE762B2-C666-4B46-8EDF-109DB09EA095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE762B2-C666-4B46-8EDF-109DB09EA095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5F8474-6E1E-4ACF-9097-C8E176F9A8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -304,13 +301,16 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>CSDN-0000000550</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +328,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -350,10 +358,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -379,8 +388,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -706,158 +717,161 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="U2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y2" t="s">
         <v>81</v>
       </c>
-      <c r="B2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="U2" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://hl--test.sandbox.lightning.force.com/lightning/r/Coverage_Sector_Dependency__c/a516e0000000gsuAAA/view" xr:uid="{0A07BB00-1434-46FA-81A9-0921524431F8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -872,18 +886,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -907,54 +921,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -994,138 +1008,138 @@
   <sheetData>
     <row r="1" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="U1" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="V2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
+++ b/TestData/TMTT0036872_VerifyTheFunctionalityOfFormForFVALightning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5F8474-6E1E-4ACF-9097-C8E176F9A8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED6EF1B-CAE4-4950-BA33-BECA9A6B2495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -288,9 +288,6 @@
     <t>9999</t>
   </si>
   <si>
-    <t>Techno Aide</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -300,10 +297,13 @@
     <t> Liz Hedgcock</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
-    <t>CSDN-0000000550</t>
+    <t>HC - Healthcare</t>
+  </si>
+  <si>
+    <t>Dental</t>
+  </si>
+  <si>
+    <t>Techno Brain Group</t>
   </si>
 </sst>
 </file>
@@ -791,10 +791,10 @@
         <v>55</v>
       </c>
       <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>91</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -897,7 +897,7 @@
         <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1076,7 @@
         <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>36</v>
@@ -1136,10 +1136,10 @@
         <v>78</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
